--- a/data/trans_dic/IP7_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP7_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general regular o mala</t>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,79</t>
+          <t>1,2; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,47</t>
+          <t>0,45; 4,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 8,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,52</t>
+          <t>0,54; 5,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,08</t>
+          <t>1,35; 6,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,22</t>
+          <t>1,52; 7,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 15,12</t>
+          <t>2,87; 15,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,53</t>
+          <t>0,58; 3,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,32</t>
+          <t>1,93; 5,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,6</t>
+          <t>1,42; 4,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,6</t>
+          <t>2,43; 8,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,06</t>
+          <t>0,25; 2,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,25</t>
+          <t>0,93; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,74</t>
+          <t>0,88; 5,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,76</t>
+          <t>0,4; 4,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,83</t>
+          <t>1,91; 5,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,05</t>
+          <t>0,24; 1,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,59</t>
+          <t>0,26; 2,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,55</t>
+          <t>0,61; 4,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,32</t>
+          <t>1,22; 3,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,42</t>
+          <t>0,73; 2,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,7</t>
+          <t>0,86; 2,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,52</t>
+          <t>0,85; 3,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,76</t>
+          <t>0,55; 5,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,22</t>
+          <t>0,85; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,58</t>
+          <t>0,48; 3,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,71</t>
+          <t>1,58; 6,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,49</t>
+          <t>3,21; 9,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,83</t>
+          <t>1,3; 5,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,49</t>
+          <t>0,85; 5,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,73</t>
+          <t>0,81; 5,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,22</t>
+          <t>2,43; 6,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,38</t>
+          <t>1,46; 4,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,32</t>
+          <t>1,0; 3,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,84</t>
+          <t>1,66; 4,94</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,6</t>
+          <t>1,57; 5,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,58</t>
+          <t>0,78; 4,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,36</t>
+          <t>0,78; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,54</t>
+          <t>1,4; 10,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,26</t>
+          <t>1,35; 5,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,08</t>
+          <t>1,92; 6,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,86</t>
+          <t>0,75; 4,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,54</t>
+          <t>0,75; 3,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,78</t>
+          <t>1,8; 4,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,92</t>
+          <t>1,75; 4,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,95</t>
+          <t>1,07; 3,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,77</t>
+          <t>1,41; 6,74</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,74</t>
+          <t>1,04; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,49</t>
+          <t>1,42; 3,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,97</t>
+          <t>1,21; 2,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,15</t>
+          <t>1,88; 6,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,9</t>
+          <t>2,61; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,56</t>
+          <t>1,7; 3,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,12</t>
+          <t>1,38; 3,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,6</t>
+          <t>1,61; 3,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,4</t>
+          <t>1,96; 3,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,16</t>
+          <t>1,83; 3,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,62</t>
+          <t>1,44; 2,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,29</t>
+          <t>2,03; 4,42</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4755</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9873</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6904</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5837</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3876</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1768; 9298</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>586; 5384</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4895</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>658; 6085</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1961; 9801</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1874; 9125</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1762; 9324</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1319; 7360</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5641; 15502</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3615; 12198</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2887; 10662</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4826</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8801</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7373</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6058</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>621; 5135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2194; 11323</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1838; 10490</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>638; 6903</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4809; 14653</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>643; 5307</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>657; 6182</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1119; 8352</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6158; 16977</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3634; 11844</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3998; 13718</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2901; 11993</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3513</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4887</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5487</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10625</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7348</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11478</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>697; 6678</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1333; 7693</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>903; 6984</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2741; 11101</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4541; 13521</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2067; 9055</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1596; 9788</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1730; 11492</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6537; 17109</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4621; 14268</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3777; 13178</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6425; 19080</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3456</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11930</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>16440</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3054; 10518</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1335; 7551</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1345; 8221</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3869; 29974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2757; 11241</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3461; 12588</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1294; 8319</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2287; 10676</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7194; 18440</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6143; 16571</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3680; 13225</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8189; 39137</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11645</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16619</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18669</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>37059</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>35346</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>28897</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>39813</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7110; 18445</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10097; 23497</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8476; 20490</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12519; 43018</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18773; 34175</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12736; 26443</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10206; 22578</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>12240; 28009</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>27470; 47114</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26744; 45809</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>20816; 38452</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>29035; 63150</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>